--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4245,6 +4245,618 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>121569086</v>
+      </c>
+      <c r="B32" t="n">
+        <v>90737</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>769076</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7118826</v>
+      </c>
+      <c r="S32" t="n">
+        <v>5</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>121569091</v>
+      </c>
+      <c r="B33" t="n">
+        <v>90719</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>769044</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7119157</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>121569092</v>
+      </c>
+      <c r="B34" t="n">
+        <v>77540</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>769029</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7119245</v>
+      </c>
+      <c r="S34" t="n">
+        <v>5</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>121569090</v>
+      </c>
+      <c r="B35" t="n">
+        <v>90719</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>768999</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7119143</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>121569089</v>
+      </c>
+      <c r="B36" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>769106</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7119075</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>121569093</v>
+      </c>
+      <c r="B37" t="n">
+        <v>78608</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Gravmark, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>769054</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7119266</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Sävar</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-07-06</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Linda Spjut</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -4247,10 +4247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121569086</v>
+        <v>121569092</v>
       </c>
       <c r="B32" t="n">
-        <v>90737</v>
+        <v>77541</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769076</v>
+        <v>769029</v>
       </c>
       <c r="R32" t="n">
-        <v>7118826</v>
+        <v>7119245</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121569091</v>
+        <v>121569086</v>
       </c>
       <c r="B33" t="n">
-        <v>90719</v>
+        <v>90738</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769044</v>
+        <v>769076</v>
       </c>
       <c r="R33" t="n">
-        <v>7119157</v>
+        <v>7118826</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121569092</v>
+        <v>121569091</v>
       </c>
       <c r="B34" t="n">
-        <v>77540</v>
+        <v>90720</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6487</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769029</v>
+        <v>769044</v>
       </c>
       <c r="R34" t="n">
-        <v>7119245</v>
+        <v>7119157</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121569090</v>
+        <v>121569089</v>
       </c>
       <c r="B35" t="n">
-        <v>90719</v>
+        <v>78609</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768999</v>
+        <v>769106</v>
       </c>
       <c r="R35" t="n">
-        <v>7119143</v>
+        <v>7119075</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121569089</v>
+        <v>121569090</v>
       </c>
       <c r="B36" t="n">
-        <v>78608</v>
+        <v>90720</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769106</v>
+        <v>768999</v>
       </c>
       <c r="R36" t="n">
-        <v>7119075</v>
+        <v>7119143</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4760,7 +4760,7 @@
         <v>121569093</v>
       </c>
       <c r="B37" t="n">
-        <v>78608</v>
+        <v>78609</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -4247,10 +4247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121569092</v>
+        <v>121569086</v>
       </c>
       <c r="B32" t="n">
-        <v>77541</v>
+        <v>90738</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6487</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769029</v>
+        <v>769076</v>
       </c>
       <c r="R32" t="n">
-        <v>7119245</v>
+        <v>7118826</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121569086</v>
+        <v>121569089</v>
       </c>
       <c r="B33" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769076</v>
+        <v>769106</v>
       </c>
       <c r="R33" t="n">
-        <v>7118826</v>
+        <v>7119075</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121569091</v>
+        <v>121569090</v>
       </c>
       <c r="B34" t="n">
         <v>90720</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769044</v>
+        <v>768999</v>
       </c>
       <c r="R34" t="n">
-        <v>7119157</v>
+        <v>7119143</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121569089</v>
+        <v>121569091</v>
       </c>
       <c r="B35" t="n">
-        <v>78609</v>
+        <v>90720</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769106</v>
+        <v>769044</v>
       </c>
       <c r="R35" t="n">
-        <v>7119075</v>
+        <v>7119157</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121569090</v>
+        <v>121569093</v>
       </c>
       <c r="B36" t="n">
-        <v>90720</v>
+        <v>78609</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768999</v>
+        <v>769054</v>
       </c>
       <c r="R36" t="n">
-        <v>7119143</v>
+        <v>7119266</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121569093</v>
+        <v>121569092</v>
       </c>
       <c r="B37" t="n">
-        <v>78609</v>
+        <v>77541</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769054</v>
+        <v>769029</v>
       </c>
       <c r="R37" t="n">
-        <v>7119266</v>
+        <v>7119245</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -4247,10 +4247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121569086</v>
+        <v>121569090</v>
       </c>
       <c r="B32" t="n">
-        <v>90738</v>
+        <v>90720</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769076</v>
+        <v>768999</v>
       </c>
       <c r="R32" t="n">
-        <v>7118826</v>
+        <v>7119143</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121569090</v>
+        <v>121569091</v>
       </c>
       <c r="B34" t="n">
         <v>90720</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768999</v>
+        <v>769044</v>
       </c>
       <c r="R34" t="n">
-        <v>7119143</v>
+        <v>7119157</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121569091</v>
+        <v>121569092</v>
       </c>
       <c r="B35" t="n">
-        <v>90720</v>
+        <v>77541</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769044</v>
+        <v>769029</v>
       </c>
       <c r="R35" t="n">
-        <v>7119157</v>
+        <v>7119245</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121569093</v>
+        <v>121569086</v>
       </c>
       <c r="B36" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769054</v>
+        <v>769076</v>
       </c>
       <c r="R36" t="n">
-        <v>7119266</v>
+        <v>7118826</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121569092</v>
+        <v>121569093</v>
       </c>
       <c r="B37" t="n">
-        <v>77541</v>
+        <v>78609</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769029</v>
+        <v>769054</v>
       </c>
       <c r="R37" t="n">
-        <v>7119245</v>
+        <v>7119266</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -4247,10 +4247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121569090</v>
+        <v>121569092</v>
       </c>
       <c r="B32" t="n">
-        <v>90720</v>
+        <v>77541</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6487</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768999</v>
+        <v>769029</v>
       </c>
       <c r="R32" t="n">
-        <v>7119143</v>
+        <v>7119245</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4349,7 +4349,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121569089</v>
+        <v>121569093</v>
       </c>
       <c r="B33" t="n">
         <v>78609</v>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769106</v>
+        <v>769054</v>
       </c>
       <c r="R33" t="n">
-        <v>7119075</v>
+        <v>7119266</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4451,7 +4451,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121569091</v>
+        <v>121569090</v>
       </c>
       <c r="B34" t="n">
         <v>90720</v>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769044</v>
+        <v>768999</v>
       </c>
       <c r="R34" t="n">
-        <v>7119157</v>
+        <v>7119143</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121569092</v>
+        <v>121569091</v>
       </c>
       <c r="B35" t="n">
-        <v>77541</v>
+        <v>90720</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769029</v>
+        <v>769044</v>
       </c>
       <c r="R35" t="n">
-        <v>7119245</v>
+        <v>7119157</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121569086</v>
+        <v>121569089</v>
       </c>
       <c r="B36" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769076</v>
+        <v>769106</v>
       </c>
       <c r="R36" t="n">
-        <v>7118826</v>
+        <v>7119075</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121569093</v>
+        <v>121569086</v>
       </c>
       <c r="B37" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769054</v>
+        <v>769076</v>
       </c>
       <c r="R37" t="n">
-        <v>7119266</v>
+        <v>7118826</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -4247,10 +4247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121569089</v>
+        <v>121569091</v>
       </c>
       <c r="B32" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769106</v>
+        <v>769044</v>
       </c>
       <c r="R32" t="n">
-        <v>7119075</v>
+        <v>7119157</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121569086</v>
+        <v>121569090</v>
       </c>
       <c r="B34" t="n">
-        <v>90746</v>
+        <v>90728</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769076</v>
+        <v>768999</v>
       </c>
       <c r="R34" t="n">
-        <v>7118826</v>
+        <v>7119143</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121569090</v>
+        <v>121569093</v>
       </c>
       <c r="B35" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768999</v>
+        <v>769054</v>
       </c>
       <c r="R35" t="n">
-        <v>7119143</v>
+        <v>7119266</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121569091</v>
+        <v>121569089</v>
       </c>
       <c r="B36" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769044</v>
+        <v>769106</v>
       </c>
       <c r="R36" t="n">
-        <v>7119157</v>
+        <v>7119075</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121569093</v>
+        <v>121569086</v>
       </c>
       <c r="B37" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769054</v>
+        <v>769076</v>
       </c>
       <c r="R37" t="n">
-        <v>7119266</v>
+        <v>7118826</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -4247,10 +4247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121569091</v>
+        <v>121569086</v>
       </c>
       <c r="B32" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769044</v>
+        <v>769076</v>
       </c>
       <c r="R32" t="n">
-        <v>7119157</v>
+        <v>7118826</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121569092</v>
+        <v>121569093</v>
       </c>
       <c r="B33" t="n">
-        <v>77548</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769029</v>
+        <v>769054</v>
       </c>
       <c r="R33" t="n">
-        <v>7119245</v>
+        <v>7119266</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121569090</v>
+        <v>121569089</v>
       </c>
       <c r="B34" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>768999</v>
+        <v>769106</v>
       </c>
       <c r="R34" t="n">
-        <v>7119143</v>
+        <v>7119075</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121569093</v>
+        <v>121569091</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769054</v>
+        <v>769044</v>
       </c>
       <c r="R35" t="n">
-        <v>7119266</v>
+        <v>7119157</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121569089</v>
+        <v>121569090</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769106</v>
+        <v>768999</v>
       </c>
       <c r="R36" t="n">
-        <v>7119075</v>
+        <v>7119143</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121569086</v>
+        <v>121569092</v>
       </c>
       <c r="B37" t="n">
-        <v>90746</v>
+        <v>77548</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769076</v>
+        <v>769029</v>
       </c>
       <c r="R37" t="n">
-        <v>7118826</v>
+        <v>7119245</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -4247,10 +4247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121569086</v>
+        <v>121569090</v>
       </c>
       <c r="B32" t="n">
-        <v>90746</v>
+        <v>90728</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769076</v>
+        <v>768999</v>
       </c>
       <c r="R32" t="n">
-        <v>7118826</v>
+        <v>7119143</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121569093</v>
+        <v>121569091</v>
       </c>
       <c r="B33" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769054</v>
+        <v>769044</v>
       </c>
       <c r="R33" t="n">
-        <v>7119266</v>
+        <v>7119157</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121569089</v>
+        <v>121569086</v>
       </c>
       <c r="B34" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769106</v>
+        <v>769076</v>
       </c>
       <c r="R34" t="n">
-        <v>7119075</v>
+        <v>7118826</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121569091</v>
+        <v>121569092</v>
       </c>
       <c r="B35" t="n">
-        <v>90728</v>
+        <v>77548</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6487</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769044</v>
+        <v>769029</v>
       </c>
       <c r="R35" t="n">
-        <v>7119157</v>
+        <v>7119245</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121569090</v>
+        <v>121569089</v>
       </c>
       <c r="B36" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768999</v>
+        <v>769106</v>
       </c>
       <c r="R36" t="n">
-        <v>7119143</v>
+        <v>7119075</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121569092</v>
+        <v>121569093</v>
       </c>
       <c r="B37" t="n">
-        <v>77548</v>
+        <v>78616</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769029</v>
+        <v>769054</v>
       </c>
       <c r="R37" t="n">
-        <v>7119245</v>
+        <v>7119266</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -4247,10 +4247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121569090</v>
+        <v>121569093</v>
       </c>
       <c r="B32" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768999</v>
+        <v>769054</v>
       </c>
       <c r="R32" t="n">
-        <v>7119143</v>
+        <v>7119266</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121569091</v>
+        <v>121569086</v>
       </c>
       <c r="B33" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769044</v>
+        <v>769076</v>
       </c>
       <c r="R33" t="n">
-        <v>7119157</v>
+        <v>7118826</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121569086</v>
+        <v>121569089</v>
       </c>
       <c r="B34" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769076</v>
+        <v>769106</v>
       </c>
       <c r="R34" t="n">
-        <v>7118826</v>
+        <v>7119075</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121569092</v>
+        <v>121569090</v>
       </c>
       <c r="B35" t="n">
-        <v>77548</v>
+        <v>90728</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6487</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769029</v>
+        <v>768999</v>
       </c>
       <c r="R35" t="n">
-        <v>7119245</v>
+        <v>7119143</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121569089</v>
+        <v>121569091</v>
       </c>
       <c r="B36" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769106</v>
+        <v>769044</v>
       </c>
       <c r="R36" t="n">
-        <v>7119075</v>
+        <v>7119157</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121569093</v>
+        <v>121569092</v>
       </c>
       <c r="B37" t="n">
-        <v>78616</v>
+        <v>77548</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6487</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769054</v>
+        <v>769029</v>
       </c>
       <c r="R37" t="n">
-        <v>7119266</v>
+        <v>7119245</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -4247,10 +4247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121569093</v>
+        <v>121569086</v>
       </c>
       <c r="B32" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769054</v>
+        <v>769076</v>
       </c>
       <c r="R32" t="n">
-        <v>7119266</v>
+        <v>7118826</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121569086</v>
+        <v>121569089</v>
       </c>
       <c r="B33" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769076</v>
+        <v>769106</v>
       </c>
       <c r="R33" t="n">
-        <v>7118826</v>
+        <v>7119075</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121569089</v>
+        <v>121569091</v>
       </c>
       <c r="B34" t="n">
-        <v>78616</v>
+        <v>90728</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769106</v>
+        <v>769044</v>
       </c>
       <c r="R34" t="n">
-        <v>7119075</v>
+        <v>7119157</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121569090</v>
+        <v>121569093</v>
       </c>
       <c r="B35" t="n">
-        <v>90728</v>
+        <v>78616</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4569,21 +4569,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>768999</v>
+        <v>769054</v>
       </c>
       <c r="R35" t="n">
-        <v>7119143</v>
+        <v>7119266</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121569091</v>
+        <v>121569090</v>
       </c>
       <c r="B36" t="n">
         <v>90728</v>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>769044</v>
+        <v>768999</v>
       </c>
       <c r="R36" t="n">
-        <v>7119157</v>
+        <v>7119143</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -4247,10 +4247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121569086</v>
+        <v>121569090</v>
       </c>
       <c r="B32" t="n">
-        <v>90746</v>
+        <v>90728</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>769076</v>
+        <v>768999</v>
       </c>
       <c r="R32" t="n">
-        <v>7118826</v>
+        <v>7119143</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4655,10 +4655,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>121569090</v>
+        <v>121569086</v>
       </c>
       <c r="B36" t="n">
-        <v>90728</v>
+        <v>90746</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4671,21 +4671,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4695,10 +4695,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>768999</v>
+        <v>769076</v>
       </c>
       <c r="R36" t="n">
-        <v>7119143</v>
+        <v>7118826</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>

--- a/artfynd/A 31252-2019 artfynd.xlsx
+++ b/artfynd/A 31252-2019 artfynd.xlsx
@@ -4247,10 +4247,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>121569090</v>
+        <v>121569093</v>
       </c>
       <c r="B32" t="n">
-        <v>90728</v>
+        <v>78629</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,21 +4263,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4287,10 +4287,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>768999</v>
+        <v>769054</v>
       </c>
       <c r="R32" t="n">
-        <v>7119143</v>
+        <v>7119266</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4349,10 +4349,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>121569089</v>
+        <v>121569091</v>
       </c>
       <c r="B33" t="n">
-        <v>78616</v>
+        <v>90742</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4365,21 +4365,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4389,10 +4389,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>769106</v>
+        <v>769044</v>
       </c>
       <c r="R33" t="n">
-        <v>7119075</v>
+        <v>7119157</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4451,10 +4451,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>121569091</v>
+        <v>121569092</v>
       </c>
       <c r="B34" t="n">
-        <v>90728</v>
+        <v>77561</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4467,21 +4467,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6487</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4491,10 +4491,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>769044</v>
+        <v>769029</v>
       </c>
       <c r="R34" t="n">
-        <v>7119157</v>
+        <v>7119245</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4553,10 +4553,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>121569093</v>
+        <v>121569089</v>
       </c>
       <c r="B35" t="n">
-        <v>78616</v>
+        <v>78629</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4593,10 +4593,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>769054</v>
+        <v>769106</v>
       </c>
       <c r="R35" t="n">
-        <v>7119266</v>
+        <v>7119075</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4658,7 +4658,7 @@
         <v>121569086</v>
       </c>
       <c r="B36" t="n">
-        <v>90746</v>
+        <v>90760</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4757,10 +4757,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>121569092</v>
+        <v>121569090</v>
       </c>
       <c r="B37" t="n">
-        <v>77548</v>
+        <v>90742</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4773,21 +4773,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6487</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4797,10 +4797,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>769029</v>
+        <v>768999</v>
       </c>
       <c r="R37" t="n">
-        <v>7119245</v>
+        <v>7119143</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
